--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56762</v>
+        <v>56764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,37 +924,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131144044</v>
+        <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56748</v>
+        <v>56764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R4" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,37 +1052,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131143868</v>
+        <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56762</v>
+        <v>56750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R5" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56748</v>
+        <v>56750</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143865</v>
+        <v>131144032</v>
       </c>
       <c r="B7" t="n">
         <v>56769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R7" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1436,37 +1436,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144032</v>
+        <v>131143865</v>
       </c>
       <c r="B8" t="n">
-        <v>56767</v>
+        <v>56771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1488,14 +1488,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R8" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,37 +924,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143868</v>
+        <v>131144044</v>
       </c>
       <c r="B4" t="n">
-        <v>56764</v>
+        <v>56751</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R4" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,37 +1052,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131144044</v>
+        <v>131143868</v>
       </c>
       <c r="B5" t="n">
-        <v>56750</v>
+        <v>56765</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R5" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56750</v>
+        <v>56751</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131144032</v>
+        <v>131143865</v>
       </c>
       <c r="B7" t="n">
-        <v>56769</v>
+        <v>56772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R7" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1436,37 +1436,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131143865</v>
+        <v>131144032</v>
       </c>
       <c r="B8" t="n">
-        <v>56771</v>
+        <v>56770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1488,14 +1488,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R8" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1308,37 +1308,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143865</v>
+        <v>131144032</v>
       </c>
       <c r="B7" t="n">
-        <v>56772</v>
+        <v>56770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R7" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1436,37 +1436,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144032</v>
+        <v>131143865</v>
       </c>
       <c r="B8" t="n">
-        <v>56770</v>
+        <v>56772</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1488,14 +1488,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R8" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -924,37 +924,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131144044</v>
+        <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56751</v>
+        <v>56765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,14 +976,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R4" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1052,37 +1052,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131143868</v>
+        <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1104,14 +1104,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R5" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56751</v>
+        <v>56752</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1308,37 +1308,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131144032</v>
+        <v>131143865</v>
       </c>
       <c r="B7" t="n">
-        <v>56770</v>
+        <v>56773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R7" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1436,37 +1436,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131143865</v>
+        <v>131144032</v>
       </c>
       <c r="B8" t="n">
-        <v>56772</v>
+        <v>56771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1488,14 +1488,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R8" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56752</v>
+        <v>56755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56752</v>
+        <v>56755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131143865</v>
       </c>
       <c r="B7" t="n">
-        <v>56773</v>
+        <v>56776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>131144032</v>
       </c>
       <c r="B8" t="n">
-        <v>56771</v>
+        <v>56774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56769</v>
+        <v>56770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56769</v>
+        <v>56770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56755</v>
+        <v>56756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56755</v>
+        <v>56756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131143865</v>
       </c>
       <c r="B7" t="n">
-        <v>56776</v>
+        <v>56777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>131144032</v>
       </c>
       <c r="B8" t="n">
-        <v>56774</v>
+        <v>56775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>131144039</v>
       </c>
       <c r="B3" t="n">
-        <v>56770</v>
+        <v>56776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>131143868</v>
       </c>
       <c r="B4" t="n">
-        <v>56770</v>
+        <v>56776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>131144044</v>
       </c>
       <c r="B5" t="n">
-        <v>56756</v>
+        <v>56762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>131143867</v>
       </c>
       <c r="B6" t="n">
-        <v>56756</v>
+        <v>56762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>131143865</v>
       </c>
       <c r="B7" t="n">
-        <v>56777</v>
+        <v>56783</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>131144032</v>
       </c>
       <c r="B8" t="n">
-        <v>56775</v>
+        <v>56781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,6 +1562,4280 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132717963</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>686725</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6600952</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132717984</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>686746</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6601249</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132717774</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>686693</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6600949</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132718087</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>686766</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6601211</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132717929</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>686684</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6600961</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132718067</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>686977</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6601142</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132718116</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>686987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6601125</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132718048</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>686877</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6601206</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132718003</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>686899</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6601196</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132718022</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>686752</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6601111</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132717927</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>686756</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6601115</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132717977</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>686762</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6601172</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132717938</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>686746</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6601001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132718075</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>686706</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6600934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132717847</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>686851</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6601149</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132717978</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>686764</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6601175</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132718020</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>686732</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6601101</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132718010</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>687004</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6601126</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132718076</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>686678</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6600948</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132717894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>686861</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6601143</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132718081</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>686773</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6601115</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132718083</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686827</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6601189</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132717854</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686989</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6601172</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132718113</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>686989</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6601147</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132717821</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>686734</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6601096</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132717755</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>686940</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6601183</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132717825</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>686752</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6601206</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132718112</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>687036</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6601152</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132718086</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>686783</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6601178</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132717979</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>686720</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6601212</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132718024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>686768</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6601040</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132717983</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>686762</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6601230</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132717827</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>686778</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6601202</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132718115</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>686958</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6601180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132717770</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>686746</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6601013</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132718077</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>686737</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6601060</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132718072</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>686714</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6600919</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132717826</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>686756</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6601161</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132718005</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>686933</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6601147</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132717761</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>687033</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6601155</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132717916</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>686752</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6601225</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1665,45 +1665,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717984</v>
+        <v>132717774</v>
       </c>
       <c r="B10" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686746</v>
+        <v>686693</v>
       </c>
       <c r="R10" t="n">
-        <v>6601249</v>
+        <v>6600949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,12 +1734,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,7 +1759,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1766,37 +1770,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1805,10 +1810,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R11" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,50 +1876,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132718087</v>
+        <v>132717984</v>
       </c>
       <c r="B12" t="n">
-        <v>58238</v>
+        <v>58353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686766</v>
+        <v>686746</v>
       </c>
       <c r="R12" t="n">
-        <v>6601211</v>
+        <v>6601249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1977,27 +1977,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132717929</v>
+        <v>132718067</v>
       </c>
       <c r="B13" t="n">
-        <v>58602</v>
+        <v>58129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>102623</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,16 +2006,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686684</v>
+        <v>686977</v>
       </c>
       <c r="R13" t="n">
-        <v>6600961</v>
+        <v>6601142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,12 +2047,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,7 +2072,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2078,27 +2083,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132718067</v>
+        <v>132717929</v>
       </c>
       <c r="B14" t="n">
-        <v>58129</v>
+        <v>58602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102623</v>
+        <v>103042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2107,21 +2112,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686977</v>
+        <v>686684</v>
       </c>
       <c r="R14" t="n">
-        <v>6601142</v>
+        <v>6600961</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2611,32 +2611,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717927</v>
+        <v>132717977</v>
       </c>
       <c r="B19" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686756</v>
+        <v>686762</v>
       </c>
       <c r="R19" t="n">
-        <v>6601115</v>
+        <v>6601172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,45 +2712,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132717977</v>
+        <v>132718075</v>
       </c>
       <c r="B20" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686762</v>
+        <v>686706</v>
       </c>
       <c r="R20" t="n">
-        <v>6601172</v>
+        <v>6600934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,12 +2782,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,7 +2807,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2813,49 +2818,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132717938</v>
+        <v>132717847</v>
       </c>
       <c r="B21" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686746</v>
+        <v>686851</v>
       </c>
       <c r="R21" t="n">
-        <v>6601001</v>
+        <v>6601149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,12 +2883,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2907,7 +2908,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2918,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132718075</v>
+        <v>132717938</v>
       </c>
       <c r="B22" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,16 +2930,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2946,10 +2947,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686706</v>
+        <v>686746</v>
       </c>
       <c r="R22" t="n">
-        <v>6600934</v>
+        <v>6601001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,32 +3024,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717847</v>
+        <v>132717927</v>
       </c>
       <c r="B23" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686851</v>
+        <v>686756</v>
       </c>
       <c r="R23" t="n">
-        <v>6601149</v>
+        <v>6601116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3543,10 +3543,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132717894</v>
+        <v>132718083</v>
       </c>
       <c r="B28" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,16 +3554,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3571,9 +3571,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3582,10 +3583,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686861</v>
+        <v>686827</v>
       </c>
       <c r="R28" t="n">
-        <v>6601143</v>
+        <v>6601189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,12 +3613,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,38 +3649,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132718081</v>
+        <v>132717894</v>
       </c>
       <c r="B29" t="n">
-        <v>58238</v>
+        <v>58636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686773</v>
+        <v>686861</v>
       </c>
       <c r="R29" t="n">
-        <v>6601115</v>
+        <v>6601143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,32 +3754,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132718083</v>
+        <v>132718081</v>
       </c>
       <c r="B30" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686827</v>
+        <v>686773</v>
       </c>
       <c r="R30" t="n">
-        <v>6601189</v>
+        <v>6601115</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132717755</v>
+        <v>132718112</v>
       </c>
       <c r="B34" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4200,9 +4200,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4211,10 +4212,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686940</v>
+        <v>687036</v>
       </c>
       <c r="R34" t="n">
-        <v>6601183</v>
+        <v>6601152</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,12 +4242,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,7 +4278,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132717825</v>
+        <v>132717755</v>
       </c>
       <c r="B35" t="n">
         <v>58636</v>
@@ -4305,17 +4306,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686752</v>
+        <v>686940</v>
       </c>
       <c r="R35" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4342,12 +4347,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4367,7 +4372,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4378,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132718112</v>
+        <v>132717825</v>
       </c>
       <c r="B36" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,16 +4394,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4407,21 +4412,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687036</v>
+        <v>686752</v>
       </c>
       <c r="R36" t="n">
-        <v>6601152</v>
+        <v>6601206</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4484,7 +4484,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132718086</v>
+        <v>132718024</v>
       </c>
       <c r="B37" t="n">
         <v>58327</v>
@@ -4512,10 +4512,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4524,10 +4528,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686783</v>
+        <v>686768</v>
       </c>
       <c r="R37" t="n">
-        <v>6601178</v>
+        <v>6601040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,12 +4558,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4691,7 +4695,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132718024</v>
+        <v>132718086</v>
       </c>
       <c r="B39" t="n">
         <v>58327</v>
@@ -4719,14 +4723,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686768</v>
+        <v>686783</v>
       </c>
       <c r="R39" t="n">
-        <v>6601040</v>
+        <v>6601178</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4801,45 +4801,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132717983</v>
+        <v>132718115</v>
       </c>
       <c r="B40" t="n">
-        <v>58353</v>
+        <v>58439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686762</v>
+        <v>686958</v>
       </c>
       <c r="R40" t="n">
-        <v>6601230</v>
+        <v>6601180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,12 +4871,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,7 +4896,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4902,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717827</v>
+        <v>132717983</v>
       </c>
       <c r="B41" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4937,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686778</v>
+        <v>686762</v>
       </c>
       <c r="R41" t="n">
-        <v>6601202</v>
+        <v>6601230</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,12 +4972,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,50 +5008,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132718115</v>
+        <v>132717827</v>
       </c>
       <c r="B42" t="n">
-        <v>58439</v>
+        <v>58602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686958</v>
+        <v>686778</v>
       </c>
       <c r="R42" t="n">
-        <v>6601180</v>
+        <v>6601202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5109,37 +5109,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132717770</v>
+        <v>132718077</v>
       </c>
       <c r="B43" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5148,10 +5149,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686746</v>
+        <v>686737</v>
       </c>
       <c r="R43" t="n">
-        <v>6601013</v>
+        <v>6601060</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,12 +5179,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,38 +5215,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132718077</v>
+        <v>132717770</v>
       </c>
       <c r="B44" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686737</v>
+        <v>686746</v>
       </c>
       <c r="R44" t="n">
-        <v>6601060</v>
+        <v>6601013</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B47" t="n">
-        <v>58238</v>
+        <v>58085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,34 +5538,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R47" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,12 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5628,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B48" t="n">
-        <v>58085</v>
+        <v>58238</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,38 +5643,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R48" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,45 +1564,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717963</v>
+        <v>132718087</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686725</v>
+        <v>686766</v>
       </c>
       <c r="R9" t="n">
-        <v>6600952</v>
+        <v>6601211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,12 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1659,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,7 +1670,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717774</v>
+        <v>132717963</v>
       </c>
       <c r="B10" t="n">
         <v>58327</v>
@@ -1693,21 +1698,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686693</v>
+        <v>686725</v>
       </c>
       <c r="R10" t="n">
-        <v>6600949</v>
+        <v>6600952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,12 +1735,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1760,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1770,38 +1771,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132718087</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
-        <v>58238</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686766</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6601211</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2501,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132718022</v>
+        <v>132717927</v>
       </c>
       <c r="B18" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2529,26 +2529,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686752</v>
+        <v>686756</v>
       </c>
       <c r="R18" t="n">
-        <v>6601111</v>
+        <v>6601115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,7 +2591,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2611,45 +2602,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717977</v>
+        <v>132717938</v>
       </c>
       <c r="B19" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686762</v>
+        <v>686746</v>
       </c>
       <c r="R19" t="n">
-        <v>6601172</v>
+        <v>6601001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2671,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2712,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718075</v>
+        <v>132718022</v>
       </c>
       <c r="B20" t="n">
         <v>58327</v>
@@ -2740,10 +2735,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2752,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686706</v>
+        <v>686752</v>
       </c>
       <c r="R20" t="n">
-        <v>6600934</v>
+        <v>6601111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,12 +2781,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,45 +2817,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132717847</v>
+        <v>132718075</v>
       </c>
       <c r="B21" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686851</v>
+        <v>686706</v>
       </c>
       <c r="R21" t="n">
-        <v>6601149</v>
+        <v>6600934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2919,49 +2923,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717938</v>
+        <v>132717847</v>
       </c>
       <c r="B22" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686746</v>
+        <v>686851</v>
       </c>
       <c r="R22" t="n">
-        <v>6601001</v>
+        <v>6601149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3024,32 +3024,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717927</v>
+        <v>132717977</v>
       </c>
       <c r="B23" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686756</v>
+        <v>686762</v>
       </c>
       <c r="R23" t="n">
-        <v>6601116</v>
+        <v>6601172</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,50 +3230,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B25" t="n">
-        <v>58636</v>
+        <v>58085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R25" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,7 +3320,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3336,45 +3331,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B26" t="n">
-        <v>58085</v>
+        <v>58636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R26" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3543,32 +3543,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132718083</v>
+        <v>132718081</v>
       </c>
       <c r="B28" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686827</v>
+        <v>686773</v>
       </c>
       <c r="R28" t="n">
-        <v>6601189</v>
+        <v>6601115</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132717894</v>
+        <v>132718083</v>
       </c>
       <c r="B29" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,16 +3660,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3677,9 +3677,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3688,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686861</v>
+        <v>686827</v>
       </c>
       <c r="R29" t="n">
-        <v>6601143</v>
+        <v>6601189</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,12 +3719,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,38 +3755,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132718081</v>
+        <v>132717894</v>
       </c>
       <c r="B30" t="n">
-        <v>58238</v>
+        <v>58636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686773</v>
+        <v>686861</v>
       </c>
       <c r="R30" t="n">
-        <v>6601115</v>
+        <v>6601143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4594,45 +4594,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132717979</v>
+        <v>132718086</v>
       </c>
       <c r="B38" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686720</v>
+        <v>686783</v>
       </c>
       <c r="R38" t="n">
-        <v>6601212</v>
+        <v>6601178</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4659,12 +4664,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4684,7 +4689,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4695,50 +4700,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132718086</v>
+        <v>132717979</v>
       </c>
       <c r="B39" t="n">
-        <v>58327</v>
+        <v>58353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686783</v>
+        <v>686720</v>
       </c>
       <c r="R39" t="n">
-        <v>6601178</v>
+        <v>6601212</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5109,38 +5109,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132718077</v>
+        <v>132717770</v>
       </c>
       <c r="B43" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5149,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686737</v>
+        <v>686746</v>
       </c>
       <c r="R43" t="n">
-        <v>6601060</v>
+        <v>6601013</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,12 +5178,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5215,37 +5214,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132717770</v>
+        <v>132718077</v>
       </c>
       <c r="B44" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686746</v>
+        <v>686737</v>
       </c>
       <c r="R44" t="n">
-        <v>6601013</v>
+        <v>6601060</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5320,50 +5320,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132718072</v>
+        <v>132717826</v>
       </c>
       <c r="B45" t="n">
-        <v>58636</v>
+        <v>58238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686714</v>
+        <v>686756</v>
       </c>
       <c r="R45" t="n">
-        <v>6600919</v>
+        <v>6601161</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5390,12 +5385,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,7 +5410,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5426,45 +5421,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132717826</v>
+        <v>132718072</v>
       </c>
       <c r="B46" t="n">
-        <v>58238</v>
+        <v>58636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686756</v>
+        <v>686714</v>
       </c>
       <c r="R46" t="n">
-        <v>6601161</v>
+        <v>6600919</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B47" t="n">
-        <v>58085</v>
+        <v>58238</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,38 +5538,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R47" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5596,12 +5592,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5621,7 +5617,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5632,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B48" t="n">
-        <v>58238</v>
+        <v>58085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,34 +5639,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R48" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,38 +1564,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132718087</v>
+        <v>132717774</v>
       </c>
       <c r="B9" t="n">
-        <v>58238</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1604,10 +1603,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686766</v>
+        <v>686693</v>
       </c>
       <c r="R9" t="n">
-        <v>6601211</v>
+        <v>6600949</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,12 +1633,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,32 +1669,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717963</v>
+        <v>132717984</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>58353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686725</v>
+        <v>686746</v>
       </c>
       <c r="R10" t="n">
-        <v>6600952</v>
+        <v>6601249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1771,37 +1770,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R11" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,32 +1876,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717984</v>
+        <v>132717963</v>
       </c>
       <c r="B12" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686746</v>
+        <v>686725</v>
       </c>
       <c r="R12" t="n">
-        <v>6601249</v>
+        <v>6600952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717927</v>
+        <v>132718022</v>
       </c>
       <c r="B18" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2529,17 +2529,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686756</v>
+        <v>686752</v>
       </c>
       <c r="R18" t="n">
-        <v>6601115</v>
+        <v>6601111</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2575,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,7 +2600,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2602,49 +2611,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717938</v>
+        <v>132717977</v>
       </c>
       <c r="B19" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686746</v>
+        <v>686762</v>
       </c>
       <c r="R19" t="n">
-        <v>6601001</v>
+        <v>6601172</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,12 +2676,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2707,7 +2712,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718022</v>
+        <v>132718075</v>
       </c>
       <c r="B20" t="n">
         <v>58327</v>
@@ -2735,14 +2740,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2751,10 +2752,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686752</v>
+        <v>686706</v>
       </c>
       <c r="R20" t="n">
-        <v>6601111</v>
+        <v>6600934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,12 +2782,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,50 +2818,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132718075</v>
+        <v>132717847</v>
       </c>
       <c r="B21" t="n">
-        <v>58327</v>
+        <v>58439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686706</v>
+        <v>686851</v>
       </c>
       <c r="R21" t="n">
-        <v>6600934</v>
+        <v>6601149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,12 +2883,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,7 +2908,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2923,32 +2919,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717847</v>
+        <v>132717927</v>
       </c>
       <c r="B22" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2958,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686851</v>
+        <v>686756</v>
       </c>
       <c r="R22" t="n">
-        <v>6601149</v>
+        <v>6601116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2984,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,45 +3020,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717977</v>
+        <v>132717938</v>
       </c>
       <c r="B23" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686762</v>
+        <v>686746</v>
       </c>
       <c r="R23" t="n">
-        <v>6601172</v>
+        <v>6601001</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3961,38 +3961,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132718113</v>
+        <v>132717821</v>
       </c>
       <c r="B32" t="n">
-        <v>58327</v>
+        <v>58353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4001,10 +4000,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686989</v>
+        <v>686734</v>
       </c>
       <c r="R32" t="n">
-        <v>6601147</v>
+        <v>6601096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,12 +4030,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,7 +4055,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4067,37 +4066,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132717821</v>
+        <v>132718113</v>
       </c>
       <c r="B33" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686734</v>
+        <v>686989</v>
       </c>
       <c r="R33" t="n">
-        <v>6601096</v>
+        <v>6601147</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132718112</v>
+        <v>132717825</v>
       </c>
       <c r="B34" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4201,21 +4201,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687036</v>
+        <v>686752</v>
       </c>
       <c r="R34" t="n">
-        <v>6601152</v>
+        <v>6601206</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,12 +4237,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4267,7 +4262,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4278,10 +4273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132717755</v>
+        <v>132718112</v>
       </c>
       <c r="B35" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,16 +4284,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4306,9 +4301,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4317,10 +4313,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686940</v>
+        <v>687036</v>
       </c>
       <c r="R35" t="n">
-        <v>6601183</v>
+        <v>6601152</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,12 +4343,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4383,7 +4379,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132717825</v>
+        <v>132717755</v>
       </c>
       <c r="B36" t="n">
         <v>58636</v>
@@ -4411,17 +4407,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686752</v>
+        <v>686940</v>
       </c>
       <c r="R36" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4484,54 +4484,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132718024</v>
+        <v>132717979</v>
       </c>
       <c r="B37" t="n">
-        <v>58327</v>
+        <v>58353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686768</v>
+        <v>686720</v>
       </c>
       <c r="R37" t="n">
-        <v>6601040</v>
+        <v>6601212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,12 +4549,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4583,7 +4574,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4700,45 +4691,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132717979</v>
+        <v>132718024</v>
       </c>
       <c r="B39" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686720</v>
+        <v>686768</v>
       </c>
       <c r="R39" t="n">
-        <v>6601212</v>
+        <v>6601040</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4801,50 +4801,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132718115</v>
+        <v>132717827</v>
       </c>
       <c r="B40" t="n">
-        <v>58439</v>
+        <v>58602</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686958</v>
+        <v>686778</v>
       </c>
       <c r="R40" t="n">
-        <v>6601180</v>
+        <v>6601202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5008,45 +5003,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132717827</v>
+        <v>132718115</v>
       </c>
       <c r="B42" t="n">
-        <v>58602</v>
+        <v>58439</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686778</v>
+        <v>686958</v>
       </c>
       <c r="R42" t="n">
-        <v>6601202</v>
+        <v>6601180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5109,37 +5109,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132717770</v>
+        <v>132718077</v>
       </c>
       <c r="B43" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5148,10 +5149,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686746</v>
+        <v>686737</v>
       </c>
       <c r="R43" t="n">
-        <v>6601013</v>
+        <v>6601060</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5178,12 +5179,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5214,38 +5215,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132718077</v>
+        <v>132717770</v>
       </c>
       <c r="B44" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686737</v>
+        <v>686746</v>
       </c>
       <c r="R44" t="n">
-        <v>6601060</v>
+        <v>6601013</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B47" t="n">
-        <v>58238</v>
+        <v>58085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,34 +5538,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R47" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,12 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5628,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B48" t="n">
-        <v>58085</v>
+        <v>58238</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,38 +5643,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R48" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,37 +1564,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1603,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R9" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,12 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,32 +1670,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717984</v>
+        <v>132717963</v>
       </c>
       <c r="B10" t="n">
-        <v>58353</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686746</v>
+        <v>686725</v>
       </c>
       <c r="R10" t="n">
-        <v>6601249</v>
+        <v>6600952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1770,38 +1771,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132718087</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
-        <v>58238</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686766</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6601211</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,32 +1876,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717963</v>
+        <v>132717984</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>58353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686725</v>
+        <v>686746</v>
       </c>
       <c r="R12" t="n">
-        <v>6600952</v>
+        <v>6601249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132718022</v>
+        <v>132717927</v>
       </c>
       <c r="B18" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2529,26 +2529,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686752</v>
+        <v>686756</v>
       </c>
       <c r="R18" t="n">
-        <v>6601111</v>
+        <v>6601116</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,7 +2591,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2611,45 +2602,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717977</v>
+        <v>132717938</v>
       </c>
       <c r="B19" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686762</v>
+        <v>686746</v>
       </c>
       <c r="R19" t="n">
-        <v>6601172</v>
+        <v>6601001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2671,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2712,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718075</v>
+        <v>132718022</v>
       </c>
       <c r="B20" t="n">
         <v>58327</v>
@@ -2740,10 +2735,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2752,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686706</v>
+        <v>686752</v>
       </c>
       <c r="R20" t="n">
-        <v>6600934</v>
+        <v>6601111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,12 +2781,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132717847</v>
+        <v>132717977</v>
       </c>
       <c r="B21" t="n">
         <v>58439</v>
@@ -2853,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686851</v>
+        <v>686762</v>
       </c>
       <c r="R21" t="n">
-        <v>6601149</v>
+        <v>6601172</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,12 +2882,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717927</v>
+        <v>132718075</v>
       </c>
       <c r="B22" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,16 +2929,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2948,16 +2947,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686756</v>
+        <v>686706</v>
       </c>
       <c r="R22" t="n">
-        <v>6601116</v>
+        <v>6600934</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2984,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3020,49 +3024,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717938</v>
+        <v>132717847</v>
       </c>
       <c r="B23" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686746</v>
+        <v>686851</v>
       </c>
       <c r="R23" t="n">
-        <v>6601001</v>
+        <v>6601149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -4172,7 +4172,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132717825</v>
+        <v>132717755</v>
       </c>
       <c r="B34" t="n">
         <v>58636</v>
@@ -4200,17 +4200,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686752</v>
+        <v>686940</v>
       </c>
       <c r="R34" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4237,12 +4241,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4262,7 +4266,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4273,10 +4277,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132718112</v>
+        <v>132717825</v>
       </c>
       <c r="B35" t="n">
-        <v>58327</v>
+        <v>58636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4284,16 +4288,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4302,21 +4306,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687036</v>
+        <v>686752</v>
       </c>
       <c r="R35" t="n">
-        <v>6601152</v>
+        <v>6601206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4343,12 +4342,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4368,7 +4367,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4379,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132717755</v>
+        <v>132718112</v>
       </c>
       <c r="B36" t="n">
-        <v>58636</v>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4390,16 +4389,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4407,9 +4406,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686940</v>
+        <v>687036</v>
       </c>
       <c r="R36" t="n">
-        <v>6601183</v>
+        <v>6601152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5109,38 +5109,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132718077</v>
+        <v>132717770</v>
       </c>
       <c r="B43" t="n">
-        <v>58439</v>
+        <v>58636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5149,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686737</v>
+        <v>686746</v>
       </c>
       <c r="R43" t="n">
-        <v>6601060</v>
+        <v>6601013</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,12 +5178,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5215,37 +5214,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132717770</v>
+        <v>132718077</v>
       </c>
       <c r="B44" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5254,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686746</v>
+        <v>686737</v>
       </c>
       <c r="R44" t="n">
-        <v>6601013</v>
+        <v>6601060</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,32 +1564,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717963</v>
+        <v>132717984</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686725</v>
+        <v>686746</v>
       </c>
       <c r="R9" t="n">
-        <v>6600952</v>
+        <v>6601249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,37 +1665,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1704,10 +1705,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R10" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,12 +1735,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,45 +1771,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717984</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686746</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6601249</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1871,50 +1876,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132718087</v>
+        <v>132717963</v>
       </c>
       <c r="B12" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686766</v>
+        <v>686725</v>
       </c>
       <c r="R12" t="n">
-        <v>6601211</v>
+        <v>6600952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2501,32 +2501,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717847</v>
+        <v>132717927</v>
       </c>
       <c r="B18" t="n">
-        <v>58444</v>
+        <v>58641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686851</v>
+        <v>686756</v>
       </c>
       <c r="R18" t="n">
-        <v>6601149</v>
+        <v>6601115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132718022</v>
+        <v>132717938</v>
       </c>
       <c r="B19" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2635,21 +2635,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686752</v>
+        <v>686746</v>
       </c>
       <c r="R19" t="n">
-        <v>6601111</v>
+        <v>6601001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2671,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2712,7 +2707,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718075</v>
+        <v>132718022</v>
       </c>
       <c r="B20" t="n">
         <v>58332</v>
@@ -2740,10 +2735,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2752,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686706</v>
+        <v>686752</v>
       </c>
       <c r="R20" t="n">
-        <v>6600934</v>
+        <v>6601111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,12 +2781,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,45 +2817,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132717977</v>
+        <v>132718075</v>
       </c>
       <c r="B21" t="n">
-        <v>58444</v>
+        <v>58332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686762</v>
+        <v>686706</v>
       </c>
       <c r="R21" t="n">
-        <v>6601172</v>
+        <v>6600934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2919,49 +2923,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717938</v>
+        <v>132717977</v>
       </c>
       <c r="B22" t="n">
-        <v>58641</v>
+        <v>58444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686746</v>
+        <v>686762</v>
       </c>
       <c r="R22" t="n">
-        <v>6601001</v>
+        <v>6601172</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3024,32 +3024,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717927</v>
+        <v>132717847</v>
       </c>
       <c r="B23" t="n">
-        <v>58641</v>
+        <v>58444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686756</v>
+        <v>686851</v>
       </c>
       <c r="R23" t="n">
-        <v>6601115</v>
+        <v>6601149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3230,50 +3230,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B25" t="n">
-        <v>58641</v>
+        <v>58090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R25" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,7 +3320,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3336,45 +3331,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B26" t="n">
-        <v>58090</v>
+        <v>58641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R26" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3543,37 +3543,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132717894</v>
+        <v>132718081</v>
       </c>
       <c r="B28" t="n">
-        <v>58641</v>
+        <v>58243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3582,10 +3583,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686861</v>
+        <v>686773</v>
       </c>
       <c r="R28" t="n">
-        <v>6601143</v>
+        <v>6601115</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,12 +3613,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,38 +3649,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132718081</v>
+        <v>132717894</v>
       </c>
       <c r="B29" t="n">
-        <v>58243</v>
+        <v>58641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686773</v>
+        <v>686861</v>
       </c>
       <c r="R29" t="n">
-        <v>6601115</v>
+        <v>6601143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4590,54 +4590,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132718024</v>
+        <v>132717979</v>
       </c>
       <c r="B38" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686768</v>
+        <v>686720</v>
       </c>
       <c r="R38" t="n">
-        <v>6601040</v>
+        <v>6601212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,12 +4655,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,7 +4680,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4700,45 +4691,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132717979</v>
+        <v>132718024</v>
       </c>
       <c r="B39" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686720</v>
+        <v>686768</v>
       </c>
       <c r="R39" t="n">
-        <v>6601212</v>
+        <v>6601040</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4801,50 +4801,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132718115</v>
+        <v>132717827</v>
       </c>
       <c r="B40" t="n">
-        <v>58444</v>
+        <v>58607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686958</v>
+        <v>686778</v>
       </c>
       <c r="R40" t="n">
-        <v>6601180</v>
+        <v>6601202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4907,32 +4902,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717827</v>
+        <v>132717983</v>
       </c>
       <c r="B41" t="n">
-        <v>58607</v>
+        <v>58358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4937,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686778</v>
+        <v>686762</v>
       </c>
       <c r="R41" t="n">
-        <v>6601202</v>
+        <v>6601230</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,12 +4967,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5008,45 +5003,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132717983</v>
+        <v>132718115</v>
       </c>
       <c r="B42" t="n">
-        <v>58358</v>
+        <v>58444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686762</v>
+        <v>686958</v>
       </c>
       <c r="R42" t="n">
-        <v>6601230</v>
+        <v>6601180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B47" t="n">
-        <v>58090</v>
+        <v>58243</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,38 +5538,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R47" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5596,12 +5592,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5621,7 +5617,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5632,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B48" t="n">
-        <v>58243</v>
+        <v>58090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,34 +5639,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R48" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,32 +1564,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717984</v>
+        <v>132717963</v>
       </c>
       <c r="B9" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686746</v>
+        <v>686725</v>
       </c>
       <c r="R9" t="n">
-        <v>6601249</v>
+        <v>6600952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1665,38 +1665,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132718087</v>
+        <v>132717774</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1705,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686766</v>
+        <v>686693</v>
       </c>
       <c r="R10" t="n">
-        <v>6601211</v>
+        <v>6600949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,12 +1734,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,49 +1770,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717774</v>
+        <v>132717984</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686693</v>
+        <v>686746</v>
       </c>
       <c r="R11" t="n">
-        <v>6600949</v>
+        <v>6601249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1835,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1860,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,45 +1871,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717963</v>
+        <v>132718087</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686725</v>
+        <v>686766</v>
       </c>
       <c r="R12" t="n">
-        <v>6600952</v>
+        <v>6601211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2184,38 +2184,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132718116</v>
+        <v>132718048</v>
       </c>
       <c r="B15" t="n">
-        <v>58332</v>
+        <v>58090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>205976</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2224,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686987</v>
+        <v>686877</v>
       </c>
       <c r="R15" t="n">
-        <v>6601125</v>
+        <v>6601206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,12 +2258,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,42 +2294,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132718048</v>
+        <v>132718116</v>
       </c>
       <c r="B16" t="n">
-        <v>58090</v>
+        <v>58332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686877</v>
+        <v>686987</v>
       </c>
       <c r="R16" t="n">
-        <v>6601206</v>
+        <v>6601125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,32 +2501,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717927</v>
+        <v>132717847</v>
       </c>
       <c r="B18" t="n">
-        <v>58641</v>
+        <v>58444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686756</v>
+        <v>686851</v>
       </c>
       <c r="R18" t="n">
-        <v>6601115</v>
+        <v>6601149</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717938</v>
+        <v>132718022</v>
       </c>
       <c r="B19" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,16 +2613,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2635,16 +2635,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686746</v>
+        <v>686752</v>
       </c>
       <c r="R19" t="n">
-        <v>6601001</v>
+        <v>6601111</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,12 +2676,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,54 +2712,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718022</v>
+        <v>132717977</v>
       </c>
       <c r="B20" t="n">
-        <v>58332</v>
+        <v>58444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686752</v>
+        <v>686762</v>
       </c>
       <c r="R20" t="n">
-        <v>6601111</v>
+        <v>6601172</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,7 +2802,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2923,32 +2919,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717977</v>
+        <v>132717927</v>
       </c>
       <c r="B22" t="n">
-        <v>58444</v>
+        <v>58641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2958,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686762</v>
+        <v>686756</v>
       </c>
       <c r="R22" t="n">
-        <v>6601172</v>
+        <v>6601116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,45 +3020,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717847</v>
+        <v>132717938</v>
       </c>
       <c r="B23" t="n">
-        <v>58444</v>
+        <v>58641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686851</v>
+        <v>686746</v>
       </c>
       <c r="R23" t="n">
-        <v>6601149</v>
+        <v>6601001</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3230,45 +3230,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B25" t="n">
-        <v>58090</v>
+        <v>58641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R25" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,12 +3300,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,7 +3325,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3331,50 +3336,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B26" t="n">
-        <v>58641</v>
+        <v>58090</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R26" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132717894</v>
+        <v>132718083</v>
       </c>
       <c r="B29" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,16 +3660,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3677,9 +3677,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3688,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686861</v>
+        <v>686827</v>
       </c>
       <c r="R29" t="n">
-        <v>6601143</v>
+        <v>6601189</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,12 +3719,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,10 +3755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132718083</v>
+        <v>132717894</v>
       </c>
       <c r="B30" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,16 +3766,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3782,10 +3783,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686827</v>
+        <v>686861</v>
       </c>
       <c r="R30" t="n">
-        <v>6601189</v>
+        <v>6601143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4590,45 +4590,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132717979</v>
+        <v>132718024</v>
       </c>
       <c r="B38" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686720</v>
+        <v>686768</v>
       </c>
       <c r="R38" t="n">
-        <v>6601212</v>
+        <v>6601040</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4655,12 +4664,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4680,7 +4689,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4691,54 +4700,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132718024</v>
+        <v>132717979</v>
       </c>
       <c r="B39" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686768</v>
+        <v>686720</v>
       </c>
       <c r="R39" t="n">
-        <v>6601040</v>
+        <v>6601212</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4801,32 +4801,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132717827</v>
+        <v>132717983</v>
       </c>
       <c r="B40" t="n">
-        <v>58607</v>
+        <v>58358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686778</v>
+        <v>686762</v>
       </c>
       <c r="R40" t="n">
-        <v>6601202</v>
+        <v>6601230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4902,32 +4902,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717983</v>
+        <v>132717827</v>
       </c>
       <c r="B41" t="n">
-        <v>58358</v>
+        <v>58607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103037</v>
+        <v>103042</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4937,10 +4937,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686762</v>
+        <v>686778</v>
       </c>
       <c r="R41" t="n">
-        <v>6601230</v>
+        <v>6601202</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,45 +1564,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717963</v>
+        <v>132718087</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686725</v>
+        <v>686766</v>
       </c>
       <c r="R9" t="n">
-        <v>6600952</v>
+        <v>6601211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,12 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1659,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,7 +1670,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717774</v>
+        <v>132717963</v>
       </c>
       <c r="B10" t="n">
         <v>58332</v>
@@ -1693,21 +1698,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686693</v>
+        <v>686725</v>
       </c>
       <c r="R10" t="n">
-        <v>6600949</v>
+        <v>6600952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,12 +1735,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1760,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1770,45 +1771,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717984</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686746</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6601249</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1871,50 +1876,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132718087</v>
+        <v>132717984</v>
       </c>
       <c r="B12" t="n">
-        <v>58243</v>
+        <v>58358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686766</v>
+        <v>686746</v>
       </c>
       <c r="R12" t="n">
-        <v>6601211</v>
+        <v>6601249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1977,27 +1977,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132718067</v>
+        <v>132717929</v>
       </c>
       <c r="B13" t="n">
-        <v>58134</v>
+        <v>58607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102623</v>
+        <v>103042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686977</v>
+        <v>686684</v>
       </c>
       <c r="R13" t="n">
-        <v>6601142</v>
+        <v>6600961</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,12 +2042,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2083,27 +2078,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132717929</v>
+        <v>132718067</v>
       </c>
       <c r="B14" t="n">
-        <v>58607</v>
+        <v>58134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>102623</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2112,16 +2107,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686684</v>
+        <v>686977</v>
       </c>
       <c r="R14" t="n">
-        <v>6600961</v>
+        <v>6601142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2184,42 +2184,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132718048</v>
+        <v>132718116</v>
       </c>
       <c r="B15" t="n">
-        <v>58090</v>
+        <v>58332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2228,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686877</v>
+        <v>686987</v>
       </c>
       <c r="R15" t="n">
-        <v>6601206</v>
+        <v>6601125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,12 +2254,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,38 +2290,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132718116</v>
+        <v>132718048</v>
       </c>
       <c r="B16" t="n">
-        <v>58332</v>
+        <v>58090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>205976</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686987</v>
+        <v>686877</v>
       </c>
       <c r="R16" t="n">
-        <v>6601125</v>
+        <v>6601206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,7 +2501,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717847</v>
+        <v>132717977</v>
       </c>
       <c r="B18" t="n">
         <v>58444</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686851</v>
+        <v>686762</v>
       </c>
       <c r="R18" t="n">
-        <v>6601149</v>
+        <v>6601172</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2602,54 +2602,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132718022</v>
+        <v>132717847</v>
       </c>
       <c r="B19" t="n">
-        <v>58332</v>
+        <v>58444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686752</v>
+        <v>686851</v>
       </c>
       <c r="R19" t="n">
-        <v>6601111</v>
+        <v>6601149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,12 +2667,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,7 +2692,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2712,45 +2703,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132717977</v>
+        <v>132718022</v>
       </c>
       <c r="B20" t="n">
-        <v>58444</v>
+        <v>58332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686762</v>
+        <v>686752</v>
       </c>
       <c r="R20" t="n">
-        <v>6601172</v>
+        <v>6601111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717927</v>
+        <v>132717938</v>
       </c>
       <c r="B22" t="n">
         <v>58641</v>
@@ -2947,17 +2947,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686756</v>
+        <v>686746</v>
       </c>
       <c r="R22" t="n">
-        <v>6601116</v>
+        <v>6601001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2984,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3020,7 +3024,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717938</v>
+        <v>132717927</v>
       </c>
       <c r="B23" t="n">
         <v>58641</v>
@@ -3048,21 +3052,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686746</v>
+        <v>686756</v>
       </c>
       <c r="R23" t="n">
-        <v>6601001</v>
+        <v>6601115</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3230,50 +3230,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B25" t="n">
-        <v>58641</v>
+        <v>58090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R25" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,7 +3320,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3336,45 +3331,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B26" t="n">
-        <v>58090</v>
+        <v>58641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R26" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3961,38 +3961,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132718113</v>
+        <v>132717821</v>
       </c>
       <c r="B32" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4001,10 +4000,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686989</v>
+        <v>686734</v>
       </c>
       <c r="R32" t="n">
-        <v>6601147</v>
+        <v>6601096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,12 +4030,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,7 +4055,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4067,37 +4066,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132717821</v>
+        <v>132718113</v>
       </c>
       <c r="B33" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686734</v>
+        <v>686989</v>
       </c>
       <c r="R33" t="n">
-        <v>6601096</v>
+        <v>6601147</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132718112</v>
+        <v>132717755</v>
       </c>
       <c r="B34" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4200,10 +4200,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4212,10 +4211,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687036</v>
+        <v>686940</v>
       </c>
       <c r="R34" t="n">
-        <v>6601152</v>
+        <v>6601183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,12 +4241,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4278,7 +4277,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132717755</v>
+        <v>132717825</v>
       </c>
       <c r="B35" t="n">
         <v>58641</v>
@@ -4306,21 +4305,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686940</v>
+        <v>686752</v>
       </c>
       <c r="R35" t="n">
-        <v>6601183</v>
+        <v>6601206</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,12 +4342,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4372,7 +4367,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4383,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132717825</v>
+        <v>132718112</v>
       </c>
       <c r="B36" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4394,16 +4389,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4412,16 +4407,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686752</v>
+        <v>687036</v>
       </c>
       <c r="R36" t="n">
-        <v>6601206</v>
+        <v>6601152</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4801,45 +4801,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132717983</v>
+        <v>132718115</v>
       </c>
       <c r="B40" t="n">
-        <v>58358</v>
+        <v>58444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686762</v>
+        <v>686958</v>
       </c>
       <c r="R40" t="n">
-        <v>6601230</v>
+        <v>6601180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,12 +4871,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,7 +4896,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4902,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717827</v>
+        <v>132717983</v>
       </c>
       <c r="B41" t="n">
-        <v>58607</v>
+        <v>58358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4937,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686778</v>
+        <v>686762</v>
       </c>
       <c r="R41" t="n">
-        <v>6601202</v>
+        <v>6601230</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,12 +4972,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,50 +5008,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132718115</v>
+        <v>132717827</v>
       </c>
       <c r="B42" t="n">
-        <v>58444</v>
+        <v>58607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686958</v>
+        <v>686778</v>
       </c>
       <c r="R42" t="n">
-        <v>6601180</v>
+        <v>6601202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,50 +1564,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132718087</v>
+        <v>132717963</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686766</v>
+        <v>686725</v>
       </c>
       <c r="R9" t="n">
-        <v>6601211</v>
+        <v>6600952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,12 +1629,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1670,7 +1665,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717963</v>
+        <v>132717774</v>
       </c>
       <c r="B10" t="n">
         <v>58332</v>
@@ -1698,17 +1693,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686725</v>
+        <v>686693</v>
       </c>
       <c r="R10" t="n">
-        <v>6600952</v>
+        <v>6600949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,12 +1734,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,7 +1759,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1771,37 +1770,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R11" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,27 +1977,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132717929</v>
+        <v>132718067</v>
       </c>
       <c r="B13" t="n">
-        <v>58607</v>
+        <v>58134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>102623</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,16 +2006,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686684</v>
+        <v>686977</v>
       </c>
       <c r="R13" t="n">
-        <v>6600961</v>
+        <v>6601142</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,12 +2047,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,7 +2072,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2078,27 +2083,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132718067</v>
+        <v>132717929</v>
       </c>
       <c r="B14" t="n">
-        <v>58134</v>
+        <v>58607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102623</v>
+        <v>103042</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2107,21 +2112,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686977</v>
+        <v>686684</v>
       </c>
       <c r="R14" t="n">
-        <v>6601142</v>
+        <v>6600961</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2184,38 +2184,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132718116</v>
+        <v>132718048</v>
       </c>
       <c r="B15" t="n">
-        <v>58332</v>
+        <v>58090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>205976</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2224,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686987</v>
+        <v>686877</v>
       </c>
       <c r="R15" t="n">
-        <v>6601125</v>
+        <v>6601206</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,12 +2258,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,42 +2294,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132718048</v>
+        <v>132718116</v>
       </c>
       <c r="B16" t="n">
-        <v>58090</v>
+        <v>58332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686877</v>
+        <v>686987</v>
       </c>
       <c r="R16" t="n">
-        <v>6601206</v>
+        <v>6601125</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717938</v>
+        <v>132717927</v>
       </c>
       <c r="B22" t="n">
         <v>58641</v>
@@ -2947,21 +2947,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686746</v>
+        <v>686756</v>
       </c>
       <c r="R22" t="n">
-        <v>6601001</v>
+        <v>6601115</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2984,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,7 +3009,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3024,7 +3020,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717927</v>
+        <v>132717938</v>
       </c>
       <c r="B23" t="n">
         <v>58641</v>
@@ -3052,17 +3048,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686756</v>
+        <v>686746</v>
       </c>
       <c r="R23" t="n">
-        <v>6601115</v>
+        <v>6601001</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3230,45 +3230,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B25" t="n">
-        <v>58090</v>
+        <v>58641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R25" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3295,12 +3300,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,7 +3325,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3331,50 +3336,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B26" t="n">
-        <v>58641</v>
+        <v>58090</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R26" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3543,38 +3543,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132718081</v>
+        <v>132717894</v>
       </c>
       <c r="B28" t="n">
-        <v>58243</v>
+        <v>58641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3583,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686773</v>
+        <v>686861</v>
       </c>
       <c r="R28" t="n">
-        <v>6601115</v>
+        <v>6601143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,12 +3612,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,37 +3754,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132717894</v>
+        <v>132718081</v>
       </c>
       <c r="B30" t="n">
-        <v>58641</v>
+        <v>58243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686861</v>
+        <v>686773</v>
       </c>
       <c r="R30" t="n">
-        <v>6601143</v>
+        <v>6601115</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,37 +3961,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132717821</v>
+        <v>132718113</v>
       </c>
       <c r="B32" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4000,10 +4001,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686734</v>
+        <v>686989</v>
       </c>
       <c r="R32" t="n">
-        <v>6601096</v>
+        <v>6601147</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4030,12 +4031,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4055,7 +4056,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4066,38 +4067,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132718113</v>
+        <v>132717821</v>
       </c>
       <c r="B33" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686989</v>
+        <v>686734</v>
       </c>
       <c r="R33" t="n">
-        <v>6601147</v>
+        <v>6601096</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132717755</v>
+        <v>132718112</v>
       </c>
       <c r="B34" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,16 +4183,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4200,9 +4200,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4211,10 +4212,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686940</v>
+        <v>687036</v>
       </c>
       <c r="R34" t="n">
-        <v>6601183</v>
+        <v>6601152</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,12 +4242,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,7 +4278,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132717825</v>
+        <v>132717755</v>
       </c>
       <c r="B35" t="n">
         <v>58641</v>
@@ -4305,17 +4306,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686752</v>
+        <v>686940</v>
       </c>
       <c r="R35" t="n">
-        <v>6601206</v>
+        <v>6601183</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4342,12 +4347,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4367,7 +4372,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4378,10 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132718112</v>
+        <v>132717825</v>
       </c>
       <c r="B36" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,16 +4394,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4407,21 +4412,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687036</v>
+        <v>686752</v>
       </c>
       <c r="R36" t="n">
-        <v>6601152</v>
+        <v>6601206</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4801,50 +4801,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132718115</v>
+        <v>132717983</v>
       </c>
       <c r="B40" t="n">
-        <v>58444</v>
+        <v>58358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103018</v>
+        <v>103037</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686958</v>
+        <v>686762</v>
       </c>
       <c r="R40" t="n">
-        <v>6601180</v>
+        <v>6601230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4907,32 +4902,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717983</v>
+        <v>132717827</v>
       </c>
       <c r="B41" t="n">
-        <v>58358</v>
+        <v>58607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103037</v>
+        <v>103042</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4937,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686762</v>
+        <v>686778</v>
       </c>
       <c r="R41" t="n">
-        <v>6601230</v>
+        <v>6601202</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,12 +4967,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5008,45 +5003,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132717827</v>
+        <v>132718115</v>
       </c>
       <c r="B42" t="n">
-        <v>58607</v>
+        <v>58444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686778</v>
+        <v>686958</v>
       </c>
       <c r="R42" t="n">
-        <v>6601202</v>
+        <v>6601180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5320,45 +5320,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132717826</v>
+        <v>132718072</v>
       </c>
       <c r="B45" t="n">
-        <v>58243</v>
+        <v>58641</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686756</v>
+        <v>686714</v>
       </c>
       <c r="R45" t="n">
-        <v>6601161</v>
+        <v>6600919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5385,12 +5390,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5410,7 +5415,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5421,50 +5426,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132718072</v>
+        <v>132717826</v>
       </c>
       <c r="B46" t="n">
-        <v>58641</v>
+        <v>58243</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686714</v>
+        <v>686756</v>
       </c>
       <c r="R46" t="n">
-        <v>6600919</v>
+        <v>6601161</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B47" t="n">
-        <v>58243</v>
+        <v>58090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,34 +5538,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R47" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,12 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5628,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B48" t="n">
-        <v>58090</v>
+        <v>58243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,38 +5643,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R48" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,45 +1564,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717963</v>
+        <v>132718087</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686725</v>
+        <v>686766</v>
       </c>
       <c r="R9" t="n">
-        <v>6600952</v>
+        <v>6601211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,12 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1659,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,49 +1670,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717774</v>
+        <v>132717984</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686693</v>
+        <v>686746</v>
       </c>
       <c r="R10" t="n">
-        <v>6600949</v>
+        <v>6601249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,12 +1735,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1760,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1770,50 +1771,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132718087</v>
+        <v>132717963</v>
       </c>
       <c r="B11" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686766</v>
+        <v>686725</v>
       </c>
       <c r="R11" t="n">
-        <v>6601211</v>
+        <v>6600952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1836,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1861,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,45 +1872,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717984</v>
+        <v>132717774</v>
       </c>
       <c r="B12" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686746</v>
+        <v>686693</v>
       </c>
       <c r="R12" t="n">
-        <v>6601249</v>
+        <v>6600949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4484,50 +4484,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132718086</v>
+        <v>132717979</v>
       </c>
       <c r="B37" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686783</v>
+        <v>686720</v>
       </c>
       <c r="R37" t="n">
-        <v>6601178</v>
+        <v>6601212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4554,12 +4549,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4579,7 +4574,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4590,7 +4585,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132718024</v>
+        <v>132718086</v>
       </c>
       <c r="B38" t="n">
         <v>58332</v>
@@ -4618,14 +4613,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4634,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686768</v>
+        <v>686783</v>
       </c>
       <c r="R38" t="n">
-        <v>6601040</v>
+        <v>6601178</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,12 +4655,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4700,45 +4691,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132717979</v>
+        <v>132718024</v>
       </c>
       <c r="B39" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686720</v>
+        <v>686768</v>
       </c>
       <c r="R39" t="n">
-        <v>6601212</v>
+        <v>6601040</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,50 +1564,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132718087</v>
+        <v>132717963</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686766</v>
+        <v>686725</v>
       </c>
       <c r="R9" t="n">
-        <v>6601211</v>
+        <v>6600952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,12 +1629,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,7 +1654,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1670,45 +1665,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717984</v>
+        <v>132718087</v>
       </c>
       <c r="B10" t="n">
-        <v>58358</v>
+        <v>58243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686746</v>
+        <v>686766</v>
       </c>
       <c r="R10" t="n">
-        <v>6601249</v>
+        <v>6601211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1771,7 +1771,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717963</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
         <v>58332</v>
@@ -1799,17 +1799,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686725</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6600952</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1872,49 +1876,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717774</v>
+        <v>132717984</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686693</v>
+        <v>686746</v>
       </c>
       <c r="R12" t="n">
-        <v>6600949</v>
+        <v>6601249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1977,27 +1977,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132718067</v>
+        <v>132717929</v>
       </c>
       <c r="B13" t="n">
-        <v>58134</v>
+        <v>58607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102623</v>
+        <v>103042</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,21 +2006,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686977</v>
+        <v>686684</v>
       </c>
       <c r="R13" t="n">
-        <v>6601142</v>
+        <v>6600961</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,12 +2042,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2083,27 +2078,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132717929</v>
+        <v>132718067</v>
       </c>
       <c r="B14" t="n">
-        <v>58607</v>
+        <v>58134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103042</v>
+        <v>102623</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2112,16 +2107,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686684</v>
+        <v>686977</v>
       </c>
       <c r="R14" t="n">
-        <v>6600961</v>
+        <v>6601142</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2184,42 +2184,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132718048</v>
+        <v>132718116</v>
       </c>
       <c r="B15" t="n">
-        <v>58090</v>
+        <v>58332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2228,10 +2224,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686877</v>
+        <v>686987</v>
       </c>
       <c r="R15" t="n">
-        <v>6601206</v>
+        <v>6601125</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,12 +2254,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,38 +2290,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132718116</v>
+        <v>132718048</v>
       </c>
       <c r="B16" t="n">
-        <v>58332</v>
+        <v>58090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>205976</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686987</v>
+        <v>686877</v>
       </c>
       <c r="R16" t="n">
-        <v>6601125</v>
+        <v>6601206</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2501,45 +2501,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717977</v>
+        <v>132718075</v>
       </c>
       <c r="B18" t="n">
-        <v>58444</v>
+        <v>58332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686762</v>
+        <v>686706</v>
       </c>
       <c r="R18" t="n">
-        <v>6601172</v>
+        <v>6600934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2571,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,7 +2596,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2703,54 +2708,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718022</v>
+        <v>132717977</v>
       </c>
       <c r="B20" t="n">
-        <v>58332</v>
+        <v>58444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686752</v>
+        <v>686762</v>
       </c>
       <c r="R20" t="n">
-        <v>6601111</v>
+        <v>6601172</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,12 +2773,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,7 +2798,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2813,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132718075</v>
+        <v>132717927</v>
       </c>
       <c r="B21" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,16 +2820,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2842,21 +2838,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686706</v>
+        <v>686756</v>
       </c>
       <c r="R21" t="n">
-        <v>6600934</v>
+        <v>6601115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2883,12 +2874,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,7 +2899,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2919,7 +2910,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717927</v>
+        <v>132717938</v>
       </c>
       <c r="B22" t="n">
         <v>58641</v>
@@ -2947,17 +2938,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686756</v>
+        <v>686746</v>
       </c>
       <c r="R22" t="n">
-        <v>6601115</v>
+        <v>6601001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2984,12 +2979,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,7 +3004,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3020,10 +3015,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717938</v>
+        <v>132718022</v>
       </c>
       <c r="B23" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,16 +3026,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3053,16 +3048,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686746</v>
+        <v>686752</v>
       </c>
       <c r="R23" t="n">
-        <v>6601001</v>
+        <v>6601111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3230,50 +3230,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718020</v>
+        <v>132718010</v>
       </c>
       <c r="B25" t="n">
-        <v>58641</v>
+        <v>58090</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>205976</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>686732</v>
+        <v>687004</v>
       </c>
       <c r="R25" t="n">
-        <v>6601101</v>
+        <v>6601126</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,7 +3320,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3336,45 +3331,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718010</v>
+        <v>132718020</v>
       </c>
       <c r="B26" t="n">
-        <v>58090</v>
+        <v>58641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>687004</v>
+        <v>686732</v>
       </c>
       <c r="R26" t="n">
-        <v>6601126</v>
+        <v>6601101</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3543,37 +3543,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132717894</v>
+        <v>132718081</v>
       </c>
       <c r="B28" t="n">
-        <v>58641</v>
+        <v>58243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3582,10 +3583,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686861</v>
+        <v>686773</v>
       </c>
       <c r="R28" t="n">
-        <v>6601143</v>
+        <v>6601115</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,12 +3613,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3754,38 +3755,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132718081</v>
+        <v>132717894</v>
       </c>
       <c r="B30" t="n">
-        <v>58243</v>
+        <v>58641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686773</v>
+        <v>686861</v>
       </c>
       <c r="R30" t="n">
-        <v>6601115</v>
+        <v>6601143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4484,45 +4484,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132717979</v>
+        <v>132718024</v>
       </c>
       <c r="B37" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686720</v>
+        <v>686768</v>
       </c>
       <c r="R37" t="n">
-        <v>6601212</v>
+        <v>6601040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,12 +4558,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4574,7 +4583,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4691,54 +4700,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132718024</v>
+        <v>132717979</v>
       </c>
       <c r="B39" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686768</v>
+        <v>686720</v>
       </c>
       <c r="R39" t="n">
-        <v>6601040</v>
+        <v>6601212</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,12 +4765,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4801,45 +4801,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132717983</v>
+        <v>132718115</v>
       </c>
       <c r="B40" t="n">
-        <v>58358</v>
+        <v>58444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686762</v>
+        <v>686958</v>
       </c>
       <c r="R40" t="n">
-        <v>6601230</v>
+        <v>6601180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,12 +4871,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,7 +4896,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4902,32 +4907,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717827</v>
+        <v>132717983</v>
       </c>
       <c r="B41" t="n">
-        <v>58607</v>
+        <v>58358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4937,10 +4942,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686778</v>
+        <v>686762</v>
       </c>
       <c r="R41" t="n">
-        <v>6601202</v>
+        <v>6601230</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4967,12 +4972,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,50 +5008,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132718115</v>
+        <v>132717827</v>
       </c>
       <c r="B42" t="n">
-        <v>58444</v>
+        <v>58607</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686958</v>
+        <v>686778</v>
       </c>
       <c r="R42" t="n">
-        <v>6601180</v>
+        <v>6601202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5320,50 +5320,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132718072</v>
+        <v>132717826</v>
       </c>
       <c r="B45" t="n">
-        <v>58641</v>
+        <v>58243</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103044</v>
+        <v>103012</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686714</v>
+        <v>686756</v>
       </c>
       <c r="R45" t="n">
-        <v>6600919</v>
+        <v>6601161</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5390,12 +5385,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5415,7 +5410,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5426,45 +5421,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132717826</v>
+        <v>132718072</v>
       </c>
       <c r="B46" t="n">
-        <v>58243</v>
+        <v>58641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686756</v>
+        <v>686714</v>
       </c>
       <c r="R46" t="n">
-        <v>6601161</v>
+        <v>6600919</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B47" t="n">
-        <v>58090</v>
+        <v>58243</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,38 +5538,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R47" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5596,12 +5592,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5621,7 +5617,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5632,10 +5628,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B48" t="n">
-        <v>58243</v>
+        <v>58090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,34 +5639,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R48" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -1564,45 +1564,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132717963</v>
+        <v>132718087</v>
       </c>
       <c r="B9" t="n">
-        <v>58332</v>
+        <v>58243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686725</v>
+        <v>686766</v>
       </c>
       <c r="R9" t="n">
-        <v>6600952</v>
+        <v>6601211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,12 +1634,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,7 +1659,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1665,38 +1670,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132718087</v>
+        <v>132717774</v>
       </c>
       <c r="B10" t="n">
-        <v>58243</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1705,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686766</v>
+        <v>686693</v>
       </c>
       <c r="R10" t="n">
-        <v>6601211</v>
+        <v>6600949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1735,12 +1739,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,49 +1775,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717774</v>
+        <v>132717984</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686693</v>
+        <v>686746</v>
       </c>
       <c r="R11" t="n">
-        <v>6600949</v>
+        <v>6601249</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,32 +1876,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717984</v>
+        <v>132717963</v>
       </c>
       <c r="B12" t="n">
-        <v>58358</v>
+        <v>58332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686746</v>
+        <v>686725</v>
       </c>
       <c r="R12" t="n">
-        <v>6601249</v>
+        <v>6600952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132718075</v>
+        <v>132717927</v>
       </c>
       <c r="B18" t="n">
-        <v>58332</v>
+        <v>58641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2530,21 +2530,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686706</v>
+        <v>686756</v>
       </c>
       <c r="R18" t="n">
-        <v>6600934</v>
+        <v>6601115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,12 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,7 +2591,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2607,45 +2602,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717847</v>
+        <v>132717938</v>
       </c>
       <c r="B19" t="n">
-        <v>58444</v>
+        <v>58641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686851</v>
+        <v>686746</v>
       </c>
       <c r="R19" t="n">
-        <v>6601149</v>
+        <v>6601001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,12 +2671,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2697,7 +2696,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2708,45 +2707,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132717977</v>
+        <v>132718022</v>
       </c>
       <c r="B20" t="n">
-        <v>58444</v>
+        <v>58332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686762</v>
+        <v>686752</v>
       </c>
       <c r="R20" t="n">
-        <v>6601172</v>
+        <v>6601111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,12 +2781,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,7 +2806,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2809,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132717927</v>
+        <v>132718075</v>
       </c>
       <c r="B21" t="n">
-        <v>58641</v>
+        <v>58332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,16 +2828,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2838,16 +2846,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686756</v>
+        <v>686706</v>
       </c>
       <c r="R21" t="n">
-        <v>6601115</v>
+        <v>6600934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2912,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2910,49 +2923,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717938</v>
+        <v>132717847</v>
       </c>
       <c r="B22" t="n">
-        <v>58641</v>
+        <v>58444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686746</v>
+        <v>686851</v>
       </c>
       <c r="R22" t="n">
-        <v>6601001</v>
+        <v>6601149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,12 +2988,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,7 +3013,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3015,54 +3024,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132718022</v>
+        <v>132717977</v>
       </c>
       <c r="B23" t="n">
-        <v>58332</v>
+        <v>58444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686752</v>
+        <v>686762</v>
       </c>
       <c r="R23" t="n">
-        <v>6601111</v>
+        <v>6601172</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -4801,50 +4801,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132718115</v>
+        <v>132717983</v>
       </c>
       <c r="B40" t="n">
-        <v>58444</v>
+        <v>58358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103018</v>
+        <v>103037</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686958</v>
+        <v>686762</v>
       </c>
       <c r="R40" t="n">
-        <v>6601180</v>
+        <v>6601230</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4871,12 +4866,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4907,32 +4902,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132717983</v>
+        <v>132717827</v>
       </c>
       <c r="B41" t="n">
-        <v>58358</v>
+        <v>58607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103037</v>
+        <v>103042</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4942,10 +4937,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686762</v>
+        <v>686778</v>
       </c>
       <c r="R41" t="n">
-        <v>6601230</v>
+        <v>6601202</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,12 +4967,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5008,45 +5003,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132717827</v>
+        <v>132718115</v>
       </c>
       <c r="B42" t="n">
-        <v>58607</v>
+        <v>58444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686778</v>
+        <v>686958</v>
       </c>
       <c r="R42" t="n">
-        <v>6601202</v>
+        <v>6601180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5527,10 +5527,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132718005</v>
+        <v>132717761</v>
       </c>
       <c r="B47" t="n">
-        <v>58243</v>
+        <v>58090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5538,34 +5538,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103012</v>
+        <v>205976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686933</v>
+        <v>687033</v>
       </c>
       <c r="R47" t="n">
-        <v>6601147</v>
+        <v>6601155</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5592,12 +5596,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5628,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132717761</v>
+        <v>132718005</v>
       </c>
       <c r="B48" t="n">
-        <v>58090</v>
+        <v>58243</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,38 +5643,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>205976</v>
+        <v>103012</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687033</v>
+        <v>686933</v>
       </c>
       <c r="R48" t="n">
-        <v>6601155</v>
+        <v>6601147</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1641189</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686782.2522835935</v>
+        <v>686782</v>
       </c>
       <c r="R2" t="n">
-        <v>6601195.367106566</v>
+        <v>6601195</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2002-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131144039</v>
+        <v>131143868</v>
       </c>
       <c r="B3" t="n">
-        <v>56776</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Båtstorps förskola, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686956</v>
+        <v>686690</v>
       </c>
       <c r="R3" t="n">
-        <v>6601143</v>
+        <v>6601110</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +867,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -892,7 +877,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -924,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131143868</v>
+        <v>131144039</v>
       </c>
       <c r="B4" t="n">
-        <v>56776</v>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,7 +939,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,14 +961,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Södra Atriumvägen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686690</v>
+        <v>686956</v>
       </c>
       <c r="R4" t="n">
-        <v>6601110</v>
+        <v>6601143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +995,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1020,7 +1005,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1052,66 +1037,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131144044</v>
+        <v>132718067</v>
       </c>
       <c r="B5" t="n">
-        <v>56762</v>
+        <v>58151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686956</v>
+        <v>686977</v>
       </c>
       <c r="R5" t="n">
-        <v>6601143</v>
+        <v>6601142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,22 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,22 +1127,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131143867</v>
+        <v>132717796</v>
       </c>
       <c r="B6" t="n">
-        <v>56762</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,55 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686690</v>
+        <v>686854</v>
       </c>
       <c r="R6" t="n">
-        <v>6601110</v>
+        <v>6601101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,22 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,22 +1228,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131143865</v>
+        <v>132717826</v>
       </c>
       <c r="B7" t="n">
-        <v>56783</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,55 +1255,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206002</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Båtstorps förskola, Upl</t>
+          <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686690</v>
+        <v>686756</v>
       </c>
       <c r="R7" t="n">
-        <v>6601110</v>
+        <v>6601161</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,22 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,78 +1329,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131144032</v>
+        <v>132718005</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>58260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205995</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Atriumvägen, Upl</t>
+          <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686956</v>
+        <v>686933</v>
       </c>
       <c r="R8" t="n">
-        <v>6601143</v>
+        <v>6601147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1522,22 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,22 +1430,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
+          <t>Jenny Hjelm Córdoba</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Berg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132718087</v>
+        <v>132718081</v>
       </c>
       <c r="B9" t="n">
-        <v>58243</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686766</v>
+        <v>686773</v>
       </c>
       <c r="R9" t="n">
-        <v>6601211</v>
+        <v>6601115</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1670,37 +1552,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132717774</v>
+        <v>132718087</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>58260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1709,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686693</v>
+        <v>686766</v>
       </c>
       <c r="R10" t="n">
-        <v>6600949</v>
+        <v>6601211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,12 +1622,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,45 +1658,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132717984</v>
+        <v>132717774</v>
       </c>
       <c r="B11" t="n">
-        <v>58358</v>
+        <v>58349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686746</v>
+        <v>686693</v>
       </c>
       <c r="R11" t="n">
-        <v>6601249</v>
+        <v>6600949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,12 +1727,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,7 +1752,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1876,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132717963</v>
+        <v>132717860</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686725</v>
+        <v>686985</v>
       </c>
       <c r="R12" t="n">
-        <v>6600952</v>
+        <v>6601090</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,12 +1828,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,27 +1864,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132717929</v>
+        <v>132717963</v>
       </c>
       <c r="B13" t="n">
-        <v>58607</v>
+        <v>58349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2012,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686684</v>
+        <v>686725</v>
       </c>
       <c r="R13" t="n">
-        <v>6600961</v>
+        <v>6600952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2078,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132718067</v>
+        <v>132718022</v>
       </c>
       <c r="B14" t="n">
-        <v>58134</v>
+        <v>58349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,16 +1976,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102623</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2106,10 +1993,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2118,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>686977</v>
+        <v>686752</v>
       </c>
       <c r="R14" t="n">
-        <v>6601142</v>
+        <v>6601111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,10 +2075,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132718116</v>
+        <v>132718024</v>
       </c>
       <c r="B15" t="n">
-        <v>58332</v>
+        <v>58349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2212,10 +2103,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2224,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>686987</v>
+        <v>686768</v>
       </c>
       <c r="R15" t="n">
-        <v>6601125</v>
+        <v>6601040</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,12 +2149,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,42 +2185,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132718048</v>
+        <v>132718075</v>
       </c>
       <c r="B16" t="n">
-        <v>58090</v>
+        <v>58349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205976</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>686877</v>
+        <v>686706</v>
       </c>
       <c r="R16" t="n">
-        <v>6601206</v>
+        <v>6600934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2255,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,45 +2291,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132718003</v>
+        <v>132718083</v>
       </c>
       <c r="B17" t="n">
-        <v>58444</v>
+        <v>58349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>686899</v>
+        <v>686827</v>
       </c>
       <c r="R17" t="n">
-        <v>6601196</v>
+        <v>6601189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,12 +2361,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,7 +2386,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2501,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132717927</v>
+        <v>132718086</v>
       </c>
       <c r="B18" t="n">
-        <v>58641</v>
+        <v>58349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,16 +2408,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2530,16 +2426,21 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>686756</v>
+        <v>686783</v>
       </c>
       <c r="R18" t="n">
-        <v>6601115</v>
+        <v>6601178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,12 +2467,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,7 +2492,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2602,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132717938</v>
+        <v>132718104</v>
       </c>
       <c r="B19" t="n">
-        <v>58641</v>
+        <v>58349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,16 +2514,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2630,9 +2531,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2641,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>686746</v>
+        <v>687039</v>
       </c>
       <c r="R19" t="n">
-        <v>6601001</v>
+        <v>6601178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,12 +2573,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,10 +2609,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132718022</v>
+        <v>132718112</v>
       </c>
       <c r="B20" t="n">
-        <v>58332</v>
+        <v>58349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,14 +2637,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2751,10 +2649,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>686752</v>
+        <v>687036</v>
       </c>
       <c r="R20" t="n">
-        <v>6601111</v>
+        <v>6601152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,12 +2679,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132718075</v>
+        <v>132718113</v>
       </c>
       <c r="B21" t="n">
-        <v>58332</v>
+        <v>58349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>686706</v>
+        <v>686989</v>
       </c>
       <c r="R21" t="n">
-        <v>6600934</v>
+        <v>6601147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,45 +2821,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132717847</v>
+        <v>132718116</v>
       </c>
       <c r="B22" t="n">
-        <v>58444</v>
+        <v>58349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>686851</v>
+        <v>686987</v>
       </c>
       <c r="R22" t="n">
-        <v>6601149</v>
+        <v>6601125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,12 +2891,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,7 +2916,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3024,45 +2927,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132717977</v>
+        <v>132718121</v>
       </c>
       <c r="B23" t="n">
-        <v>58444</v>
+        <v>58349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>686762</v>
+        <v>686971</v>
       </c>
       <c r="R23" t="n">
-        <v>6601172</v>
+        <v>6601111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3089,12 +2997,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,7 +3022,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3125,49 +3033,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132717978</v>
+        <v>132717847</v>
       </c>
       <c r="B24" t="n">
-        <v>58090</v>
+        <v>58461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205976</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>686764</v>
+        <v>686851</v>
       </c>
       <c r="R24" t="n">
-        <v>6601175</v>
+        <v>6601149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3194,12 +3098,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,32 +3134,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132718010</v>
+        <v>132717965</v>
       </c>
       <c r="B25" t="n">
-        <v>58090</v>
+        <v>58461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205976</v>
+        <v>103018</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3265,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>687004</v>
+        <v>686766</v>
       </c>
       <c r="R25" t="n">
-        <v>6601126</v>
+        <v>6600969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132718020</v>
+        <v>132717977</v>
       </c>
       <c r="B26" t="n">
-        <v>58641</v>
+        <v>58461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,39 +3246,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>686732</v>
+        <v>686762</v>
       </c>
       <c r="R26" t="n">
-        <v>6601101</v>
+        <v>6601172</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,12 +3300,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3325,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3437,14 +3336,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132718076</v>
+        <v>132718003</v>
       </c>
       <c r="B27" t="n">
-        <v>58444</v>
+        <v>58461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3466,21 +3365,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>686678</v>
+        <v>686899</v>
       </c>
       <c r="R27" t="n">
-        <v>6600948</v>
+        <v>6601196</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,12 +3401,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,7 +3426,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3543,32 +3437,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132718081</v>
+        <v>132718071</v>
       </c>
       <c r="B28" t="n">
-        <v>58243</v>
+        <v>58461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3583,10 +3477,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>686773</v>
+        <v>686738</v>
       </c>
       <c r="R28" t="n">
-        <v>6601115</v>
+        <v>6600912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3649,10 +3543,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132718083</v>
+        <v>132718076</v>
       </c>
       <c r="B29" t="n">
-        <v>58332</v>
+        <v>58461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3660,21 +3554,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3689,10 +3583,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>686827</v>
+        <v>686678</v>
       </c>
       <c r="R29" t="n">
-        <v>6601189</v>
+        <v>6600948</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3755,10 +3649,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132717894</v>
+        <v>132718077</v>
       </c>
       <c r="B30" t="n">
-        <v>58641</v>
+        <v>58461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,26 +3660,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3794,10 +3689,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686861</v>
+        <v>686737</v>
       </c>
       <c r="R30" t="n">
-        <v>6601143</v>
+        <v>6601060</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3824,12 +3719,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,45 +3755,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132717854</v>
+        <v>132718115</v>
       </c>
       <c r="B31" t="n">
-        <v>58607</v>
+        <v>58461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103042</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686989</v>
+        <v>686958</v>
       </c>
       <c r="R31" t="n">
-        <v>6601172</v>
+        <v>6601180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3925,12 +3825,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3950,7 +3850,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3961,10 +3861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132718113</v>
+        <v>132717855</v>
       </c>
       <c r="B32" t="n">
-        <v>58332</v>
+        <v>58131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3972,16 +3872,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>103023</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3990,21 +3890,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686989</v>
+        <v>687014</v>
       </c>
       <c r="R32" t="n">
-        <v>6601147</v>
+        <v>6601163</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,12 +3926,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,7 +3951,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4070,7 +3965,7 @@
         <v>132717821</v>
       </c>
       <c r="B33" t="n">
-        <v>58358</v>
+        <v>58375</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,38 +4067,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132718112</v>
+        <v>132717916</v>
       </c>
       <c r="B34" t="n">
-        <v>58332</v>
+        <v>58375</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4212,10 +4106,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687036</v>
+        <v>686752</v>
       </c>
       <c r="R34" t="n">
-        <v>6601152</v>
+        <v>6601225</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4242,12 +4136,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4278,49 +4172,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132717755</v>
+        <v>132717967</v>
       </c>
       <c r="B35" t="n">
-        <v>58641</v>
+        <v>58375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>103037</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686940</v>
+        <v>686796</v>
       </c>
       <c r="R35" t="n">
-        <v>6601183</v>
+        <v>6601040</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,12 +4237,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4372,7 +4262,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4383,32 +4273,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132717825</v>
+        <v>132717970</v>
       </c>
       <c r="B36" t="n">
-        <v>58641</v>
+        <v>58375</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>103037</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4418,10 +4308,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686752</v>
+        <v>686795</v>
       </c>
       <c r="R36" t="n">
-        <v>6601206</v>
+        <v>6601053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,12 +4338,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,54 +4374,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132718024</v>
+        <v>132717973</v>
       </c>
       <c r="B37" t="n">
-        <v>58332</v>
+        <v>58375</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686768</v>
+        <v>686816</v>
       </c>
       <c r="R37" t="n">
-        <v>6601040</v>
+        <v>6601077</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,12 +4439,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4583,7 +4464,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4594,50 +4475,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132718086</v>
+        <v>132717979</v>
       </c>
       <c r="B38" t="n">
-        <v>58332</v>
+        <v>58375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>103037</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686783</v>
+        <v>686720</v>
       </c>
       <c r="R38" t="n">
-        <v>6601178</v>
+        <v>6601212</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,12 +4540,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,7 +4565,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4700,10 +4576,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132717979</v>
+        <v>132717983</v>
       </c>
       <c r="B39" t="n">
-        <v>58358</v>
+        <v>58375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4735,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686720</v>
+        <v>686762</v>
       </c>
       <c r="R39" t="n">
-        <v>6601212</v>
+        <v>6601230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4801,10 +4677,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132717983</v>
+        <v>132717984</v>
       </c>
       <c r="B40" t="n">
-        <v>58358</v>
+        <v>58375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4836,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686762</v>
+        <v>686746</v>
       </c>
       <c r="R40" t="n">
-        <v>6601230</v>
+        <v>6601249</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4905,11 +4781,11 @@
         <v>132717827</v>
       </c>
       <c r="B41" t="n">
-        <v>58607</v>
+        <v>58624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5003,50 +4879,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132718115</v>
+        <v>132717854</v>
       </c>
       <c r="B42" t="n">
-        <v>58444</v>
+        <v>58624</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686958</v>
+        <v>686989</v>
       </c>
       <c r="R42" t="n">
-        <v>6601180</v>
+        <v>6601172</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,12 +4944,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5098,7 +4969,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5109,38 +4980,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132718077</v>
+        <v>132717885</v>
       </c>
       <c r="B43" t="n">
-        <v>58444</v>
+        <v>58624</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103018</v>
+        <v>103042</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5149,10 +5019,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>686737</v>
+        <v>686800</v>
       </c>
       <c r="R43" t="n">
-        <v>6601060</v>
+        <v>6601059</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5179,12 +5049,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5215,27 +5085,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132717770</v>
+        <v>132717929</v>
       </c>
       <c r="B44" t="n">
-        <v>58641</v>
+        <v>58624</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5243,21 +5113,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686746</v>
+        <v>686684</v>
       </c>
       <c r="R44" t="n">
-        <v>6601013</v>
+        <v>6600961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5284,12 +5150,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5309,7 +5175,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Albin Berglund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5320,32 +5186,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132717826</v>
+        <v>132718000</v>
       </c>
       <c r="B45" t="n">
-        <v>58243</v>
+        <v>58624</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103012</v>
+        <v>103042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5355,10 +5221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>686756</v>
+        <v>686903</v>
       </c>
       <c r="R45" t="n">
-        <v>6601161</v>
+        <v>6601231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5385,12 +5251,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,10 +5287,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132718072</v>
+        <v>132717754</v>
       </c>
       <c r="B46" t="n">
-        <v>58641</v>
+        <v>58658</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5449,10 +5315,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5461,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686714</v>
+        <v>687026</v>
       </c>
       <c r="R46" t="n">
-        <v>6600919</v>
+        <v>6601122</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5491,12 +5356,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5527,32 +5392,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132717761</v>
+        <v>132717755</v>
       </c>
       <c r="B47" t="n">
-        <v>58090</v>
+        <v>58658</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>205976</v>
+        <v>103044</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5566,10 +5431,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687033</v>
+        <v>686940</v>
       </c>
       <c r="R47" t="n">
-        <v>6601155</v>
+        <v>6601183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5632,45 +5497,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132718005</v>
+        <v>132717770</v>
       </c>
       <c r="B48" t="n">
-        <v>58243</v>
+        <v>58658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103012</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686933</v>
+        <v>686746</v>
       </c>
       <c r="R48" t="n">
-        <v>6601147</v>
+        <v>6601013</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5697,12 +5566,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5722,7 +5591,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Albin Berglund</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5733,39 +5602,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132717916</v>
+        <v>132717825</v>
       </c>
       <c r="B49" t="n">
-        <v>58358</v>
+        <v>58658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103037</v>
+        <v>103044</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skogsbo, Upl</t>
@@ -5775,7 +5640,7 @@
         <v>686752</v>
       </c>
       <c r="R49" t="n">
-        <v>6601225</v>
+        <v>6601206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5802,12 +5667,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5827,14 +5692,1580 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132717894</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>686861</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6601143</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
           <t>Mova Hebert</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
+      <c r="AY50" t="inlineStr">
         <is>
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132717927</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>686756</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6601116</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132717938</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>686746</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6601001</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132718020</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>686732</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6601101</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132718060</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>686915</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6601215</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132718072</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>686714</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6600919</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132717761</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>687033</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6601155</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132717978</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>686764</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6601175</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132718010</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>687004</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6601126</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Albin Berglund</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132718048</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skogsbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>686877</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6601206</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jenny Hjelm Córdoba</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mova Hebert</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>C2250234 Skogsbo artinventering 2025-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131144032</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Södra Atriumvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>686956</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6601143</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131143867</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Båtstorps förskola, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>686690</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6601110</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131144038</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Södra Atriumvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>686956</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6601143</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131143865</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Båtstorps förskola, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>686690</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6601110</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3919-2023 artfynd.xlsx
+++ b/artfynd/A 3919-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1641189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143868</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718067</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717796</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718005</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718087</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717774</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717860</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717963</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718022</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2182,6 +2252,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718024</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718075</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718083</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718086</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2606,6 +2696,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718104</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718112</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2818,6 +2918,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718113</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718116</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3030,6 +3140,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718121</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3131,6 +3246,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717847</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3232,6 +3352,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717965</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3333,6 +3458,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717977</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3434,6 +3564,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718071</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718076</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3752,6 +3897,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718077</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3858,6 +4008,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3959,6 +4114,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717855</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4064,6 +4224,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717821</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4169,6 +4334,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717916</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4270,6 +4440,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717967</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4371,6 +4546,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717970</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4472,6 +4652,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717973</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4573,6 +4758,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717979</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4674,6 +4864,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717983</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4775,6 +4970,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717984</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4876,6 +5076,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717827</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4977,6 +5182,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717854</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5082,6 +5292,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717885</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5183,6 +5398,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717929</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5284,6 +5504,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718000</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5389,6 +5614,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717754</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5494,6 +5724,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717755</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5599,6 +5834,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717770</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5700,6 +5940,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717825</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5805,6 +6050,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717894</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5906,6 +6156,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717927</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6011,6 +6266,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717938</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6117,6 +6377,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718020</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6227,6 +6492,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718060</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6333,6 +6603,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718072</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6438,6 +6713,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717761</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6543,6 +6823,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717978</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6644,6 +6929,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718010</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6754,6 +7044,11 @@
           <t>C2250234 Skogsbo artinventering 2025-2026</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718048</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6882,6 +7177,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7010,6 +7310,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143867</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7138,6 +7443,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131144038</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7266,8 +7576,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143865</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>